--- a/outputs/019f3e2b-c0a9-73a2-bab3-c0bf76811cd3/site-feature-tracker.xlsx
+++ b/outputs/019f3e2b-c0a9-73a2-bab3-c0bf76811cd3/site-feature-tracker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6a99224bd3f2469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="R0e6dc08913ea4c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R688089f66c7549d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="Rb6f642b05bec44c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -700,14 +700,14 @@
         <x:v>Feature Rows</x:v>
       </x:c>
       <x:c r="B3" s="34" t="n">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="20"/>
       <x:c r="D3" s="46" t="str">
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="E3" s="46" t="n">
-        <x:f>COUNTIF(Features!$G$2:$G$22,"Not Tested")</x:f>
+        <x:f>COUNTIF(Features!$G$2:$G$24,"Not Tested")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="20"/>
@@ -724,8 +724,8 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="E4" s="46" t="n">
-        <x:f>COUNTIF(Features!$G$2:$G$22,"Pass")</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTIF(Features!$G$2:$G$24,"Pass")</x:f>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F4" s="20"/>
     </x:row>
@@ -740,7 +740,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="E5" s="47" t="n">
-        <x:f>COUNTIF(Features!$G$2:$G$22,"Fail")</x:f>
+        <x:f>COUNTIF(Features!$G$2:$G$24,"Fail")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -749,14 +749,14 @@
         <x:v>Last Refresh</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
-        <x:v>2026-07-07 20:17:24 UTC</x:v>
+        <x:v>2026-07-07 20:23:29 UTC</x:v>
       </x:c>
       <x:c r="D6" s="47" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="E6" s="47" t="n">
-        <x:f>COUNTIF(Features!$G$2:$G$22,"Blocked")</x:f>
-        <x:v>2</x:v>
+        <x:f>COUNTIF(Features!$G$2:$G$24,"Blocked")</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -770,7 +770,7 @@
         <x:v>Pending Fix</x:v>
       </x:c>
       <x:c r="E7" s="47" t="n">
-        <x:f>COUNTIF(Features!$J$2:$J$22,"Pending")</x:f>
+        <x:f>COUNTIF(Features!$J$2:$J$24,"Pending")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -779,7 +779,7 @@
         <x:v>Fixed</x:v>
       </x:c>
       <x:c r="E8" s="47" t="n">
-        <x:f>COUNTIF(Features!$J$2:$J$22,"Fixed")</x:f>
+        <x:f>COUNTIF(Features!$J$2:$J$24,"Fixed")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -788,7 +788,7 @@
         <x:v>Not Retested</x:v>
       </x:c>
       <x:c r="E9" s="47" t="n">
-        <x:f>COUNTIF(Features!$L$2:$L$22,"Not Retested")</x:f>
+        <x:f>COUNTIF(Features!$L$2:$L$24,"Not Retested")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -797,8 +797,8 @@
         <x:v>Retest Pass</x:v>
       </x:c>
       <x:c r="E10" s="47" t="n">
-        <x:f>COUNTIF(Features!$L$2:$L$22,"Pass")</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTIF(Features!$L$2:$L$24,"Pass")</x:f>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1433,23 +1433,19 @@
         <x:v>contact/index.md; contact-success/index.md</x:v>
       </x:c>
       <x:c r="G16" s="12" t="str">
-        <x:v>Blocked</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="str">
-        <x:v>External form submission not exercised because it would send data to Formspree. Markup, required fields, and success target verified.</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="str">
-        <x:v>Low</x:v>
-      </x:c>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str"/>
+      <x:c r="I16" s="12" t="str"/>
       <x:c r="J16" s="12" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Not Needed</x:v>
       </x:c>
       <x:c r="K16" s="12" t="str"/>
       <x:c r="L16" s="12" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M16" s="13" t="str">
-        <x:v>Safe local verification completed; end-to-end submission requires explicit approval.</x:v>
+        <x:v>End-to-end browser flow verified on the current build through a local mock POST target that preserves the site form markup and redirects to /contact-success/ without sending external data.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1583,23 +1579,19 @@
         <x:v>assets/js/scripts.js</x:v>
       </x:c>
       <x:c r="G20" s="12" t="str">
-        <x:v>Blocked</x:v>
-      </x:c>
-      <x:c r="H20" s="12" t="str">
-        <x:v>No current published page in the built site uses linked image anchors, so the lightbox code path could not be exercised from live content.</x:v>
-      </x:c>
-      <x:c r="I20" s="12" t="str">
-        <x:v>Low</x:v>
-      </x:c>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str"/>
+      <x:c r="I20" s="12" t="str"/>
       <x:c r="J20" s="12" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Not Needed</x:v>
       </x:c>
       <x:c r="K20" s="12" t="str"/>
       <x:c r="L20" s="12" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M20" s="13" t="str">
-        <x:v>Static search over _site_goaltest found no a[href$=.jpg|.png|.gif] examples to test.</x:v>
+        <x:v>Verified with a local fixture page that uses the site JS and a linked PNG asset; the anchor received image-popup and opened a visible Magnific Popup overlay.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1638,67 +1630,137 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="14" t="str">
+      <x:c r="A22" s="11" t="str">
         <x:v>F-021</x:v>
       </x:c>
-      <x:c r="B22" s="15" t="str">
+      <x:c r="B22" s="12" t="str">
         <x:v>Machine-readable Outputs</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="12" t="str">
         <x:v>/feed.xml; /sitemap.xml; /llms.txt</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="D22" s="12" t="str">
         <x:v>As a reader or crawler using feed and machine-readable endpoints, I can access the site's published discovery files.</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="12" t="str">
         <x:v>The site publishes feed.xml, sitemap.xml, and llms.txt, and links to those outputs from the page head where configured.</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str">
+      <x:c r="F22" s="12" t="str">
         <x:v>_includes/head.html; README.md; scripts/build-llms-ctx-full.rb</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="H22" s="15" t="str"/>
-      <x:c r="I22" s="15" t="str"/>
-      <x:c r="J22" s="15" t="str">
-        <x:v>Not Needed</x:v>
-      </x:c>
-      <x:c r="K22" s="15" t="str"/>
-      <x:c r="L22" s="15" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M22" s="16" t="str">
+      <x:c r="G22" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="str"/>
+      <x:c r="I22" s="12" t="str"/>
+      <x:c r="J22" s="12" t="str">
+        <x:v>Not Needed</x:v>
+      </x:c>
+      <x:c r="K22" s="12" t="str"/>
+      <x:c r="L22" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M22" s="13" t="str">
         <x:v>Direct checks returned HTTP 200 for /feed.xml, /sitemap.xml, and /llms.txt.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="11" t="str">
+        <x:v>F-022</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>Math Rendering</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>/os-7-fundamentos-do-maximalismo-do-bitcoin/</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="str">
+        <x:v>As a reader on a math-heavy post, I can read equations rendered as math instead of raw TeX syntax.</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>Pages load the MathJax script when site.mathjax is enabled, and math expressions are transformed from raw source syntax into rendered output.</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>_layouts/post.html; _layouts/page.html; _config.yml; _posts/2023-05-26-os-7-fundamentos-do-maximalismo-do-bitcoin.md</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="str"/>
+      <x:c r="I23" s="12" t="str"/>
+      <x:c r="J23" s="12" t="str">
+        <x:v>Not Needed</x:v>
+      </x:c>
+      <x:c r="K23" s="12" t="str"/>
+      <x:c r="L23" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M23" s="13" t="str">
+        <x:v>Retest confirmed the MathJax script is present on the post route and the raw inline TeX sequence is no longer visible in page text.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>F-023</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="str">
+        <x:v>X/Twitter Embeds</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="str">
+        <x:v>/twitter-fixture.html</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
+        <x:v>As a reader on a page that embeds a tweet, I can see the embedded post render instead of only a plain blockquote fallback.</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="str">
+        <x:v>The site loads widgets.js and blockquote.twitter-tweet content hydrates into an embedded widget iframe when the page contains a tweet embed.</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="str">
+        <x:v>_includes/scripts.html</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="str"/>
+      <x:c r="I24" s="15" t="str"/>
+      <x:c r="J24" s="15" t="str">
+        <x:v>Not Needed</x:v>
+      </x:c>
+      <x:c r="K24" s="15" t="str"/>
+      <x:c r="L24" s="15" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M24" s="16" t="str">
+        <x:v>Verified with a local fixture page that loads the site scripts plus widgets.js; the page rendered a Twitter widget iframe.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
+  <x:conditionalFormatting sqref="G2:G24">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pass"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Fail"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Blocked"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J2:J22">
+  <x:conditionalFormatting sqref="J2:J24">
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Fixed"/>
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Pending"/>
     <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Blocked"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="L2:L22">
+  <x:conditionalFormatting sqref="L2:L24">
     <x:cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Pass"/>
     <x:cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="Fail"/>
     <x:cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Blocked"/>
   </x:conditionalFormatting>
   <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="G2:G22">
+    <x:dataValidation type="list" sqref="G2:G24">
       <x:formula1>"Not Tested,Pass,Fail,Blocked"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I2:I22">
+    <x:dataValidation type="list" sqref="I2:I24">
       <x:formula1>",Low,Medium,High"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J22">
+    <x:dataValidation type="list" sqref="J2:J24">
       <x:formula1>"Not Needed Yet,Not Needed,Pending,Fixed,Blocked"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="L2:L22">
+    <x:dataValidation type="list" sqref="L2:L24">
       <x:formula1>"Not Retested,Pass,Fail,Blocked"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
